--- a/historical_reference_data/Box_A_B_Test/cleaned/UNKNOWN950425_052029_0001VRP_BOX_A_TEST_CLEANED.xlsx
+++ b/historical_reference_data/Box_A_B_Test/cleaned/UNKNOWN950425_052029_0001VRP_BOX_A_TEST_CLEANED.xlsx
@@ -614,7 +614,11 @@
       <c r="A2" t="n">
         <v>1</v>
       </c>
-      <c r="B2" t="inlineStr"/>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>OPEN</t>
+        </is>
+      </c>
       <c r="C2" t="n">
         <v>20</v>
       </c>
@@ -722,7 +726,11 @@
       <c r="A3" t="n">
         <v>2</v>
       </c>
-      <c r="B3" t="inlineStr"/>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>START</t>
+        </is>
+      </c>
       <c r="C3" t="n">
         <v>1032</v>
       </c>
@@ -830,7 +838,11 @@
       <c r="A4" t="n">
         <v>3</v>
       </c>
-      <c r="B4" t="inlineStr"/>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>PURGE</t>
+        </is>
+      </c>
       <c r="C4" t="n">
         <v>1042</v>
       </c>
@@ -938,7 +950,11 @@
       <c r="A5" t="n">
         <v>3</v>
       </c>
-      <c r="B5" t="inlineStr"/>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>PURGE</t>
+        </is>
+      </c>
       <c r="C5" t="n">
         <v>1142</v>
       </c>
@@ -1046,7 +1062,11 @@
       <c r="A6" t="n">
         <v>3</v>
       </c>
-      <c r="B6" t="inlineStr"/>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>PURGE</t>
+        </is>
+      </c>
       <c r="C6" t="n">
         <v>1242</v>
       </c>
@@ -1154,7 +1174,11 @@
       <c r="A7" t="n">
         <v>3</v>
       </c>
-      <c r="B7" t="inlineStr"/>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>PURGE</t>
+        </is>
+      </c>
       <c r="C7" t="n">
         <v>1342</v>
       </c>
@@ -1262,7 +1286,11 @@
       <c r="A8" t="n">
         <v>3</v>
       </c>
-      <c r="B8" t="inlineStr"/>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>PURGE</t>
+        </is>
+      </c>
       <c r="C8" t="n">
         <v>1442</v>
       </c>
@@ -1370,7 +1398,11 @@
       <c r="A9" t="n">
         <v>3</v>
       </c>
-      <c r="B9" t="inlineStr"/>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>PURGE</t>
+        </is>
+      </c>
       <c r="C9" t="n">
         <v>1542</v>
       </c>
@@ -1478,7 +1510,11 @@
       <c r="A10" t="n">
         <v>3</v>
       </c>
-      <c r="B10" t="inlineStr"/>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>PURGE</t>
+        </is>
+      </c>
       <c r="C10" t="n">
         <v>1642</v>
       </c>
@@ -1586,7 +1622,11 @@
       <c r="A11" t="n">
         <v>3</v>
       </c>
-      <c r="B11" t="inlineStr"/>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>PURGE</t>
+        </is>
+      </c>
       <c r="C11" t="n">
         <v>1742</v>
       </c>
@@ -1694,7 +1734,11 @@
       <c r="A12" t="n">
         <v>3</v>
       </c>
-      <c r="B12" t="inlineStr"/>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>PURGE</t>
+        </is>
+      </c>
       <c r="C12" t="n">
         <v>1842</v>
       </c>
@@ -1802,7 +1846,11 @@
       <c r="A13" t="n">
         <v>3</v>
       </c>
-      <c r="B13" t="inlineStr"/>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>PURGE</t>
+        </is>
+      </c>
       <c r="C13" t="n">
         <v>1942</v>
       </c>
@@ -1910,7 +1958,11 @@
       <c r="A14" t="n">
         <v>3</v>
       </c>
-      <c r="B14" t="inlineStr"/>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>PURGE</t>
+        </is>
+      </c>
       <c r="C14" t="n">
         <v>2042</v>
       </c>
@@ -2018,7 +2070,11 @@
       <c r="A15" t="n">
         <v>3</v>
       </c>
-      <c r="B15" t="inlineStr"/>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>PURGE</t>
+        </is>
+      </c>
       <c r="C15" t="n">
         <v>2142</v>
       </c>
@@ -2126,7 +2182,11 @@
       <c r="A16" t="n">
         <v>3</v>
       </c>
-      <c r="B16" t="inlineStr"/>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>PURGE</t>
+        </is>
+      </c>
       <c r="C16" t="n">
         <v>2242</v>
       </c>
@@ -2234,7 +2294,11 @@
       <c r="A17" t="n">
         <v>3</v>
       </c>
-      <c r="B17" t="inlineStr"/>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>PURGE</t>
+        </is>
+      </c>
       <c r="C17" t="n">
         <v>2342</v>
       </c>
@@ -2342,7 +2406,11 @@
       <c r="A18" t="n">
         <v>3</v>
       </c>
-      <c r="B18" t="inlineStr"/>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>PURGE</t>
+        </is>
+      </c>
       <c r="C18" t="n">
         <v>2442</v>
       </c>
@@ -2450,7 +2518,11 @@
       <c r="A19" t="n">
         <v>3</v>
       </c>
-      <c r="B19" t="inlineStr"/>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>PURGE</t>
+        </is>
+      </c>
       <c r="C19" t="n">
         <v>2542</v>
       </c>
@@ -2558,7 +2630,11 @@
       <c r="A20" t="n">
         <v>3</v>
       </c>
-      <c r="B20" t="inlineStr"/>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>PURGE</t>
+        </is>
+      </c>
       <c r="C20" t="n">
         <v>2642</v>
       </c>
@@ -2666,7 +2742,11 @@
       <c r="A21" t="n">
         <v>3</v>
       </c>
-      <c r="B21" t="inlineStr"/>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>PURGE</t>
+        </is>
+      </c>
       <c r="C21" t="n">
         <v>2742</v>
       </c>
@@ -2774,7 +2854,11 @@
       <c r="A22" t="n">
         <v>3</v>
       </c>
-      <c r="B22" t="inlineStr"/>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>PURGE</t>
+        </is>
+      </c>
       <c r="C22" t="n">
         <v>2842</v>
       </c>
@@ -2882,7 +2966,11 @@
       <c r="A23" t="n">
         <v>3</v>
       </c>
-      <c r="B23" t="inlineStr"/>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>PURGE</t>
+        </is>
+      </c>
       <c r="C23" t="n">
         <v>2942</v>
       </c>
@@ -2990,7 +3078,11 @@
       <c r="A24" t="n">
         <v>3</v>
       </c>
-      <c r="B24" t="inlineStr"/>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>PURGE</t>
+        </is>
+      </c>
       <c r="C24" t="n">
         <v>3042</v>
       </c>
@@ -3098,7 +3190,11 @@
       <c r="A25" t="n">
         <v>3</v>
       </c>
-      <c r="B25" t="inlineStr"/>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>PURGE</t>
+        </is>
+      </c>
       <c r="C25" t="n">
         <v>3142</v>
       </c>
@@ -3206,7 +3302,11 @@
       <c r="A26" t="n">
         <v>3</v>
       </c>
-      <c r="B26" t="inlineStr"/>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>PURGE</t>
+        </is>
+      </c>
       <c r="C26" t="n">
         <v>3242</v>
       </c>
@@ -3314,7 +3414,11 @@
       <c r="A27" t="n">
         <v>3</v>
       </c>
-      <c r="B27" t="inlineStr"/>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>PURGE</t>
+        </is>
+      </c>
       <c r="C27" t="n">
         <v>3342</v>
       </c>
@@ -3422,7 +3526,11 @@
       <c r="A28" t="n">
         <v>3</v>
       </c>
-      <c r="B28" t="inlineStr"/>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>PURGE</t>
+        </is>
+      </c>
       <c r="C28" t="n">
         <v>3442</v>
       </c>
@@ -3530,7 +3638,11 @@
       <c r="A29" t="n">
         <v>3</v>
       </c>
-      <c r="B29" t="inlineStr"/>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>PURGE</t>
+        </is>
+      </c>
       <c r="C29" t="n">
         <v>3542</v>
       </c>
@@ -3638,7 +3750,11 @@
       <c r="A30" t="n">
         <v>3</v>
       </c>
-      <c r="B30" t="inlineStr"/>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>PURGE</t>
+        </is>
+      </c>
       <c r="C30" t="n">
         <v>3642</v>
       </c>
@@ -3746,7 +3862,11 @@
       <c r="A31" t="n">
         <v>3</v>
       </c>
-      <c r="B31" t="inlineStr"/>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>PURGE</t>
+        </is>
+      </c>
       <c r="C31" t="n">
         <v>3742</v>
       </c>
@@ -3854,7 +3974,11 @@
       <c r="A32" t="n">
         <v>3</v>
       </c>
-      <c r="B32" t="inlineStr"/>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>PURGE</t>
+        </is>
+      </c>
       <c r="C32" t="n">
         <v>3842</v>
       </c>
@@ -3962,7 +4086,11 @@
       <c r="A33" t="n">
         <v>3</v>
       </c>
-      <c r="B33" t="inlineStr"/>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>PURGE</t>
+        </is>
+      </c>
       <c r="C33" t="n">
         <v>3942</v>
       </c>
@@ -4070,7 +4198,11 @@
       <c r="A34" t="n">
         <v>3</v>
       </c>
-      <c r="B34" t="inlineStr"/>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>PURGE</t>
+        </is>
+      </c>
       <c r="C34" t="n">
         <v>4042</v>
       </c>
@@ -4178,7 +4310,11 @@
       <c r="A35" t="n">
         <v>3</v>
       </c>
-      <c r="B35" t="inlineStr"/>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>PURGE</t>
+        </is>
+      </c>
       <c r="C35" t="n">
         <v>4142</v>
       </c>
@@ -4286,7 +4422,11 @@
       <c r="A36" t="n">
         <v>3</v>
       </c>
-      <c r="B36" t="inlineStr"/>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>PURGE</t>
+        </is>
+      </c>
       <c r="C36" t="n">
         <v>4242</v>
       </c>
@@ -4394,7 +4534,11 @@
       <c r="A37" t="n">
         <v>3</v>
       </c>
-      <c r="B37" t="inlineStr"/>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>PURGE</t>
+        </is>
+      </c>
       <c r="C37" t="n">
         <v>4342</v>
       </c>
@@ -4502,7 +4646,11 @@
       <c r="A38" t="n">
         <v>3</v>
       </c>
-      <c r="B38" t="inlineStr"/>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>PURGE</t>
+        </is>
+      </c>
       <c r="C38" t="n">
         <v>4442</v>
       </c>
@@ -4610,7 +4758,11 @@
       <c r="A39" t="n">
         <v>3</v>
       </c>
-      <c r="B39" t="inlineStr"/>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>PURGE</t>
+        </is>
+      </c>
       <c r="C39" t="n">
         <v>4542</v>
       </c>
@@ -4718,7 +4870,11 @@
       <c r="A40" t="n">
         <v>3</v>
       </c>
-      <c r="B40" t="inlineStr"/>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>PURGE</t>
+        </is>
+      </c>
       <c r="C40" t="n">
         <v>4642</v>
       </c>
@@ -4826,7 +4982,11 @@
       <c r="A41" t="n">
         <v>3</v>
       </c>
-      <c r="B41" t="inlineStr"/>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>PURGE</t>
+        </is>
+      </c>
       <c r="C41" t="n">
         <v>4742</v>
       </c>
@@ -4934,7 +5094,11 @@
       <c r="A42" t="n">
         <v>3</v>
       </c>
-      <c r="B42" t="inlineStr"/>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>PURGE</t>
+        </is>
+      </c>
       <c r="C42" t="n">
         <v>4842</v>
       </c>
@@ -5042,7 +5206,11 @@
       <c r="A43" t="n">
         <v>3</v>
       </c>
-      <c r="B43" t="inlineStr"/>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>PURGE</t>
+        </is>
+      </c>
       <c r="C43" t="n">
         <v>4942</v>
       </c>
@@ -5150,7 +5318,11 @@
       <c r="A44" t="n">
         <v>3</v>
       </c>
-      <c r="B44" t="inlineStr"/>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>PURGE</t>
+        </is>
+      </c>
       <c r="C44" t="n">
         <v>5042</v>
       </c>
@@ -5258,7 +5430,11 @@
       <c r="A45" t="n">
         <v>3</v>
       </c>
-      <c r="B45" t="inlineStr"/>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>PURGE</t>
+        </is>
+      </c>
       <c r="C45" t="n">
         <v>5142</v>
       </c>
@@ -5366,7 +5542,11 @@
       <c r="A46" t="n">
         <v>3</v>
       </c>
-      <c r="B46" t="inlineStr"/>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>PURGE</t>
+        </is>
+      </c>
       <c r="C46" t="n">
         <v>5242</v>
       </c>
@@ -5474,7 +5654,11 @@
       <c r="A47" t="n">
         <v>3</v>
       </c>
-      <c r="B47" t="inlineStr"/>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>PURGE</t>
+        </is>
+      </c>
       <c r="C47" t="n">
         <v>5342</v>
       </c>
@@ -5582,7 +5766,11 @@
       <c r="A48" t="n">
         <v>3</v>
       </c>
-      <c r="B48" t="inlineStr"/>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>PURGE</t>
+        </is>
+      </c>
       <c r="C48" t="n">
         <v>5442</v>
       </c>
@@ -5690,7 +5878,11 @@
       <c r="A49" t="n">
         <v>3</v>
       </c>
-      <c r="B49" t="inlineStr"/>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>PURGE</t>
+        </is>
+      </c>
       <c r="C49" t="n">
         <v>5542</v>
       </c>
@@ -5798,7 +5990,11 @@
       <c r="A50" t="n">
         <v>3</v>
       </c>
-      <c r="B50" t="inlineStr"/>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>PURGE</t>
+        </is>
+      </c>
       <c r="C50" t="n">
         <v>5642</v>
       </c>
@@ -5906,7 +6102,11 @@
       <c r="A51" t="n">
         <v>3</v>
       </c>
-      <c r="B51" t="inlineStr"/>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>PURGE</t>
+        </is>
+      </c>
       <c r="C51" t="n">
         <v>5742</v>
       </c>
@@ -6014,7 +6214,11 @@
       <c r="A52" t="n">
         <v>3</v>
       </c>
-      <c r="B52" t="inlineStr"/>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>PURGE</t>
+        </is>
+      </c>
       <c r="C52" t="n">
         <v>5842</v>
       </c>
@@ -6122,7 +6326,11 @@
       <c r="A53" t="n">
         <v>3</v>
       </c>
-      <c r="B53" t="inlineStr"/>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>PURGE</t>
+        </is>
+      </c>
       <c r="C53" t="n">
         <v>5942</v>
       </c>
@@ -6230,7 +6438,11 @@
       <c r="A54" t="n">
         <v>3</v>
       </c>
-      <c r="B54" t="inlineStr"/>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>PURGE</t>
+        </is>
+      </c>
       <c r="C54" t="n">
         <v>6042</v>
       </c>
@@ -6338,7 +6550,11 @@
       <c r="A55" t="n">
         <v>3</v>
       </c>
-      <c r="B55" t="inlineStr"/>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>PURGE</t>
+        </is>
+      </c>
       <c r="C55" t="n">
         <v>6142</v>
       </c>
@@ -6446,7 +6662,11 @@
       <c r="A56" t="n">
         <v>3</v>
       </c>
-      <c r="B56" t="inlineStr"/>
+      <c r="B56" t="inlineStr">
+        <is>
+          <t>PURGE</t>
+        </is>
+      </c>
       <c r="C56" t="n">
         <v>6242</v>
       </c>
@@ -6554,7 +6774,11 @@
       <c r="A57" t="n">
         <v>3</v>
       </c>
-      <c r="B57" t="inlineStr"/>
+      <c r="B57" t="inlineStr">
+        <is>
+          <t>PURGE</t>
+        </is>
+      </c>
       <c r="C57" t="n">
         <v>6342</v>
       </c>
@@ -6662,7 +6886,11 @@
       <c r="A58" t="n">
         <v>3</v>
       </c>
-      <c r="B58" t="inlineStr"/>
+      <c r="B58" t="inlineStr">
+        <is>
+          <t>PURGE</t>
+        </is>
+      </c>
       <c r="C58" t="n">
         <v>6442</v>
       </c>
@@ -6770,7 +6998,11 @@
       <c r="A59" t="n">
         <v>3</v>
       </c>
-      <c r="B59" t="inlineStr"/>
+      <c r="B59" t="inlineStr">
+        <is>
+          <t>PURGE</t>
+        </is>
+      </c>
       <c r="C59" t="n">
         <v>6542</v>
       </c>
@@ -6878,7 +7110,11 @@
       <c r="A60" t="n">
         <v>3</v>
       </c>
-      <c r="B60" t="inlineStr"/>
+      <c r="B60" t="inlineStr">
+        <is>
+          <t>PURGE</t>
+        </is>
+      </c>
       <c r="C60" t="n">
         <v>6642</v>
       </c>
@@ -6986,7 +7222,11 @@
       <c r="A61" t="n">
         <v>3</v>
       </c>
-      <c r="B61" t="inlineStr"/>
+      <c r="B61" t="inlineStr">
+        <is>
+          <t>PURGE</t>
+        </is>
+      </c>
       <c r="C61" t="n">
         <v>6742</v>
       </c>
@@ -7094,7 +7334,11 @@
       <c r="A62" t="n">
         <v>3</v>
       </c>
-      <c r="B62" t="inlineStr"/>
+      <c r="B62" t="inlineStr">
+        <is>
+          <t>PURGE</t>
+        </is>
+      </c>
       <c r="C62" t="n">
         <v>6842</v>
       </c>
@@ -7202,7 +7446,11 @@
       <c r="A63" t="n">
         <v>3</v>
       </c>
-      <c r="B63" t="inlineStr"/>
+      <c r="B63" t="inlineStr">
+        <is>
+          <t>PURGE</t>
+        </is>
+      </c>
       <c r="C63" t="n">
         <v>6942</v>
       </c>
@@ -7310,7 +7558,11 @@
       <c r="A64" t="n">
         <v>3</v>
       </c>
-      <c r="B64" t="inlineStr"/>
+      <c r="B64" t="inlineStr">
+        <is>
+          <t>PURGE</t>
+        </is>
+      </c>
       <c r="C64" t="n">
         <v>7042</v>
       </c>
@@ -7418,7 +7670,11 @@
       <c r="A65" t="n">
         <v>3</v>
       </c>
-      <c r="B65" t="inlineStr"/>
+      <c r="B65" t="inlineStr">
+        <is>
+          <t>PURGE</t>
+        </is>
+      </c>
       <c r="C65" t="n">
         <v>7142</v>
       </c>
@@ -7526,7 +7782,11 @@
       <c r="A66" t="n">
         <v>3</v>
       </c>
-      <c r="B66" t="inlineStr"/>
+      <c r="B66" t="inlineStr">
+        <is>
+          <t>PURGE</t>
+        </is>
+      </c>
       <c r="C66" t="n">
         <v>7242</v>
       </c>
@@ -7634,7 +7894,11 @@
       <c r="A67" t="n">
         <v>3</v>
       </c>
-      <c r="B67" t="inlineStr"/>
+      <c r="B67" t="inlineStr">
+        <is>
+          <t>PURGE</t>
+        </is>
+      </c>
       <c r="C67" t="n">
         <v>7342</v>
       </c>
@@ -7742,7 +8006,11 @@
       <c r="A68" t="n">
         <v>3</v>
       </c>
-      <c r="B68" t="inlineStr"/>
+      <c r="B68" t="inlineStr">
+        <is>
+          <t>PURGE</t>
+        </is>
+      </c>
       <c r="C68" t="n">
         <v>7442</v>
       </c>
@@ -7850,7 +8118,11 @@
       <c r="A69" t="n">
         <v>3</v>
       </c>
-      <c r="B69" t="inlineStr"/>
+      <c r="B69" t="inlineStr">
+        <is>
+          <t>PURGE</t>
+        </is>
+      </c>
       <c r="C69" t="n">
         <v>7542</v>
       </c>
@@ -7958,7 +8230,11 @@
       <c r="A70" t="n">
         <v>3</v>
       </c>
-      <c r="B70" t="inlineStr"/>
+      <c r="B70" t="inlineStr">
+        <is>
+          <t>PURGE</t>
+        </is>
+      </c>
       <c r="C70" t="n">
         <v>7642</v>
       </c>
@@ -8066,7 +8342,11 @@
       <c r="A71" t="n">
         <v>3</v>
       </c>
-      <c r="B71" t="inlineStr"/>
+      <c r="B71" t="inlineStr">
+        <is>
+          <t>PURGE</t>
+        </is>
+      </c>
       <c r="C71" t="n">
         <v>7742</v>
       </c>
@@ -8174,7 +8454,11 @@
       <c r="A72" t="n">
         <v>3</v>
       </c>
-      <c r="B72" t="inlineStr"/>
+      <c r="B72" t="inlineStr">
+        <is>
+          <t>PURGE</t>
+        </is>
+      </c>
       <c r="C72" t="n">
         <v>7842</v>
       </c>
@@ -8282,7 +8566,11 @@
       <c r="A73" t="n">
         <v>3</v>
       </c>
-      <c r="B73" t="inlineStr"/>
+      <c r="B73" t="inlineStr">
+        <is>
+          <t>PURGE</t>
+        </is>
+      </c>
       <c r="C73" t="n">
         <v>7942</v>
       </c>
@@ -8390,7 +8678,11 @@
       <c r="A74" t="n">
         <v>3</v>
       </c>
-      <c r="B74" t="inlineStr"/>
+      <c r="B74" t="inlineStr">
+        <is>
+          <t>PURGE</t>
+        </is>
+      </c>
       <c r="C74" t="n">
         <v>8042</v>
       </c>
@@ -8498,7 +8790,11 @@
       <c r="A75" t="n">
         <v>3</v>
       </c>
-      <c r="B75" t="inlineStr"/>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>PURGE</t>
+        </is>
+      </c>
       <c r="C75" t="n">
         <v>8142</v>
       </c>
@@ -8606,7 +8902,11 @@
       <c r="A76" t="n">
         <v>3</v>
       </c>
-      <c r="B76" t="inlineStr"/>
+      <c r="B76" t="inlineStr">
+        <is>
+          <t>PURGE</t>
+        </is>
+      </c>
       <c r="C76" t="n">
         <v>8242</v>
       </c>
@@ -8714,7 +9014,11 @@
       <c r="A77" t="n">
         <v>3</v>
       </c>
-      <c r="B77" t="inlineStr"/>
+      <c r="B77" t="inlineStr">
+        <is>
+          <t>PURGE</t>
+        </is>
+      </c>
       <c r="C77" t="n">
         <v>8342</v>
       </c>
@@ -8822,7 +9126,11 @@
       <c r="A78" t="n">
         <v>3</v>
       </c>
-      <c r="B78" t="inlineStr"/>
+      <c r="B78" t="inlineStr">
+        <is>
+          <t>PURGE</t>
+        </is>
+      </c>
       <c r="C78" t="n">
         <v>8442</v>
       </c>
@@ -8930,7 +9238,11 @@
       <c r="A79" t="n">
         <v>3</v>
       </c>
-      <c r="B79" t="inlineStr"/>
+      <c r="B79" t="inlineStr">
+        <is>
+          <t>PURGE</t>
+        </is>
+      </c>
       <c r="C79" t="n">
         <v>8542</v>
       </c>
@@ -9038,7 +9350,11 @@
       <c r="A80" t="n">
         <v>3</v>
       </c>
-      <c r="B80" t="inlineStr"/>
+      <c r="B80" t="inlineStr">
+        <is>
+          <t>PURGE</t>
+        </is>
+      </c>
       <c r="C80" t="n">
         <v>8642</v>
       </c>
@@ -9146,7 +9462,11 @@
       <c r="A81" t="n">
         <v>3</v>
       </c>
-      <c r="B81" t="inlineStr"/>
+      <c r="B81" t="inlineStr">
+        <is>
+          <t>PURGE</t>
+        </is>
+      </c>
       <c r="C81" t="n">
         <v>8742</v>
       </c>
@@ -9254,7 +9574,11 @@
       <c r="A82" t="n">
         <v>3</v>
       </c>
-      <c r="B82" t="inlineStr"/>
+      <c r="B82" t="inlineStr">
+        <is>
+          <t>PURGE</t>
+        </is>
+      </c>
       <c r="C82" t="n">
         <v>8842</v>
       </c>
@@ -9362,7 +9686,11 @@
       <c r="A83" t="n">
         <v>3</v>
       </c>
-      <c r="B83" t="inlineStr"/>
+      <c r="B83" t="inlineStr">
+        <is>
+          <t>PURGE</t>
+        </is>
+      </c>
       <c r="C83" t="n">
         <v>8942</v>
       </c>
@@ -9470,7 +9798,11 @@
       <c r="A84" t="n">
         <v>3</v>
       </c>
-      <c r="B84" t="inlineStr"/>
+      <c r="B84" t="inlineStr">
+        <is>
+          <t>PURGE</t>
+        </is>
+      </c>
       <c r="C84" t="n">
         <v>9042</v>
       </c>
@@ -9578,7 +9910,11 @@
       <c r="A85" t="n">
         <v>3</v>
       </c>
-      <c r="B85" t="inlineStr"/>
+      <c r="B85" t="inlineStr">
+        <is>
+          <t>PURGE</t>
+        </is>
+      </c>
       <c r="C85" t="n">
         <v>9142</v>
       </c>
@@ -9686,7 +10022,11 @@
       <c r="A86" t="n">
         <v>3</v>
       </c>
-      <c r="B86" t="inlineStr"/>
+      <c r="B86" t="inlineStr">
+        <is>
+          <t>PURGE</t>
+        </is>
+      </c>
       <c r="C86" t="n">
         <v>9242</v>
       </c>
@@ -9794,7 +10134,11 @@
       <c r="A87" t="n">
         <v>3</v>
       </c>
-      <c r="B87" t="inlineStr"/>
+      <c r="B87" t="inlineStr">
+        <is>
+          <t>PURGE</t>
+        </is>
+      </c>
       <c r="C87" t="n">
         <v>9342</v>
       </c>
@@ -9902,7 +10246,11 @@
       <c r="A88" t="n">
         <v>3</v>
       </c>
-      <c r="B88" t="inlineStr"/>
+      <c r="B88" t="inlineStr">
+        <is>
+          <t>PURGE</t>
+        </is>
+      </c>
       <c r="C88" t="n">
         <v>9442</v>
       </c>
@@ -10010,7 +10358,11 @@
       <c r="A89" t="n">
         <v>3</v>
       </c>
-      <c r="B89" t="inlineStr"/>
+      <c r="B89" t="inlineStr">
+        <is>
+          <t>PURGE</t>
+        </is>
+      </c>
       <c r="C89" t="n">
         <v>9542</v>
       </c>
@@ -10118,7 +10470,11 @@
       <c r="A90" t="n">
         <v>3</v>
       </c>
-      <c r="B90" t="inlineStr"/>
+      <c r="B90" t="inlineStr">
+        <is>
+          <t>PURGE</t>
+        </is>
+      </c>
       <c r="C90" t="n">
         <v>9642</v>
       </c>
@@ -10226,7 +10582,11 @@
       <c r="A91" t="n">
         <v>3</v>
       </c>
-      <c r="B91" t="inlineStr"/>
+      <c r="B91" t="inlineStr">
+        <is>
+          <t>PURGE</t>
+        </is>
+      </c>
       <c r="C91" t="n">
         <v>9742</v>
       </c>
@@ -10334,7 +10694,11 @@
       <c r="A92" t="n">
         <v>3</v>
       </c>
-      <c r="B92" t="inlineStr"/>
+      <c r="B92" t="inlineStr">
+        <is>
+          <t>PURGE</t>
+        </is>
+      </c>
       <c r="C92" t="n">
         <v>9842</v>
       </c>
@@ -10442,7 +10806,11 @@
       <c r="A93" t="n">
         <v>3</v>
       </c>
-      <c r="B93" t="inlineStr"/>
+      <c r="B93" t="inlineStr">
+        <is>
+          <t>PURGE</t>
+        </is>
+      </c>
       <c r="C93" t="n">
         <v>9942</v>
       </c>
@@ -10550,7 +10918,11 @@
       <c r="A94" t="n">
         <v>3</v>
       </c>
-      <c r="B94" t="inlineStr"/>
+      <c r="B94" t="inlineStr">
+        <is>
+          <t>PURGE</t>
+        </is>
+      </c>
       <c r="C94" t="n">
         <v>10042</v>
       </c>
@@ -10658,7 +11030,11 @@
       <c r="A95" t="n">
         <v>3</v>
       </c>
-      <c r="B95" t="inlineStr"/>
+      <c r="B95" t="inlineStr">
+        <is>
+          <t>PURGE</t>
+        </is>
+      </c>
       <c r="C95" t="n">
         <v>10142</v>
       </c>
@@ -10766,7 +11142,11 @@
       <c r="A96" t="n">
         <v>3</v>
       </c>
-      <c r="B96" t="inlineStr"/>
+      <c r="B96" t="inlineStr">
+        <is>
+          <t>PURGE</t>
+        </is>
+      </c>
       <c r="C96" t="n">
         <v>10242</v>
       </c>
@@ -10874,7 +11254,11 @@
       <c r="A97" t="n">
         <v>3</v>
       </c>
-      <c r="B97" t="inlineStr"/>
+      <c r="B97" t="inlineStr">
+        <is>
+          <t>PURGE</t>
+        </is>
+      </c>
       <c r="C97" t="n">
         <v>10342</v>
       </c>
@@ -10982,7 +11366,11 @@
       <c r="A98" t="n">
         <v>3</v>
       </c>
-      <c r="B98" t="inlineStr"/>
+      <c r="B98" t="inlineStr">
+        <is>
+          <t>PURGE</t>
+        </is>
+      </c>
       <c r="C98" t="n">
         <v>10442</v>
       </c>
@@ -11090,7 +11478,11 @@
       <c r="A99" t="n">
         <v>3</v>
       </c>
-      <c r="B99" t="inlineStr"/>
+      <c r="B99" t="inlineStr">
+        <is>
+          <t>PURGE</t>
+        </is>
+      </c>
       <c r="C99" t="n">
         <v>10542</v>
       </c>
@@ -11198,7 +11590,11 @@
       <c r="A100" t="n">
         <v>3</v>
       </c>
-      <c r="B100" t="inlineStr"/>
+      <c r="B100" t="inlineStr">
+        <is>
+          <t>PURGE</t>
+        </is>
+      </c>
       <c r="C100" t="n">
         <v>10642</v>
       </c>
@@ -11306,7 +11702,11 @@
       <c r="A101" t="n">
         <v>3</v>
       </c>
-      <c r="B101" t="inlineStr"/>
+      <c r="B101" t="inlineStr">
+        <is>
+          <t>PURGE</t>
+        </is>
+      </c>
       <c r="C101" t="n">
         <v>10742</v>
       </c>
@@ -11414,7 +11814,11 @@
       <c r="A102" t="n">
         <v>3</v>
       </c>
-      <c r="B102" t="inlineStr"/>
+      <c r="B102" t="inlineStr">
+        <is>
+          <t>PURGE</t>
+        </is>
+      </c>
       <c r="C102" t="n">
         <v>10842</v>
       </c>
@@ -11522,7 +11926,11 @@
       <c r="A103" t="n">
         <v>3</v>
       </c>
-      <c r="B103" t="inlineStr"/>
+      <c r="B103" t="inlineStr">
+        <is>
+          <t>PURGE</t>
+        </is>
+      </c>
       <c r="C103" t="n">
         <v>10942</v>
       </c>
@@ -11630,7 +12038,11 @@
       <c r="A104" t="n">
         <v>3</v>
       </c>
-      <c r="B104" t="inlineStr"/>
+      <c r="B104" t="inlineStr">
+        <is>
+          <t>PURGE</t>
+        </is>
+      </c>
       <c r="C104" t="n">
         <v>11042</v>
       </c>
@@ -11738,7 +12150,11 @@
       <c r="A105" t="n">
         <v>4</v>
       </c>
-      <c r="B105" t="inlineStr"/>
+      <c r="B105" t="inlineStr">
+        <is>
+          <t>CLOSE</t>
+        </is>
+      </c>
       <c r="C105" t="n">
         <v>11052</v>
       </c>
@@ -11846,7 +12262,11 @@
       <c r="A106" t="n">
         <v>5</v>
       </c>
-      <c r="B106" t="inlineStr"/>
+      <c r="B106" t="inlineStr">
+        <is>
+          <t>CHANGE</t>
+        </is>
+      </c>
       <c r="C106" t="n">
         <v>12064</v>
       </c>
@@ -11954,7 +12374,11 @@
       <c r="A107" t="n">
         <v>6</v>
       </c>
-      <c r="B107" t="inlineStr"/>
+      <c r="B107" t="inlineStr">
+        <is>
+          <t>OPEN</t>
+        </is>
+      </c>
       <c r="C107" t="n">
         <v>12074</v>
       </c>
@@ -12062,7 +12486,11 @@
       <c r="A108" t="n">
         <v>7</v>
       </c>
-      <c r="B108" t="inlineStr"/>
+      <c r="B108" t="inlineStr">
+        <is>
+          <t>BREATH</t>
+        </is>
+      </c>
       <c r="C108" t="n">
         <v>13086</v>
       </c>
@@ -12170,7 +12598,11 @@
       <c r="A109" t="n">
         <v>7</v>
       </c>
-      <c r="B109" t="inlineStr"/>
+      <c r="B109" t="inlineStr">
+        <is>
+          <t>BREATH</t>
+        </is>
+      </c>
       <c r="C109" t="n">
         <v>13186</v>
       </c>
@@ -12278,7 +12710,11 @@
       <c r="A110" t="n">
         <v>7</v>
       </c>
-      <c r="B110" t="inlineStr"/>
+      <c r="B110" t="inlineStr">
+        <is>
+          <t>BREATH</t>
+        </is>
+      </c>
       <c r="C110" t="n">
         <v>13286</v>
       </c>
@@ -12386,7 +12822,11 @@
       <c r="A111" t="n">
         <v>7</v>
       </c>
-      <c r="B111" t="inlineStr"/>
+      <c r="B111" t="inlineStr">
+        <is>
+          <t>BREATH</t>
+        </is>
+      </c>
       <c r="C111" t="n">
         <v>13386</v>
       </c>
@@ -12494,7 +12934,11 @@
       <c r="A112" t="n">
         <v>7</v>
       </c>
-      <c r="B112" t="inlineStr"/>
+      <c r="B112" t="inlineStr">
+        <is>
+          <t>BREATH</t>
+        </is>
+      </c>
       <c r="C112" t="n">
         <v>13486</v>
       </c>
@@ -12602,7 +13046,11 @@
       <c r="A113" t="n">
         <v>7</v>
       </c>
-      <c r="B113" t="inlineStr"/>
+      <c r="B113" t="inlineStr">
+        <is>
+          <t>BREATH</t>
+        </is>
+      </c>
       <c r="C113" t="n">
         <v>13586</v>
       </c>
@@ -12710,7 +13158,11 @@
       <c r="A114" t="n">
         <v>7</v>
       </c>
-      <c r="B114" t="inlineStr"/>
+      <c r="B114" t="inlineStr">
+        <is>
+          <t>BREATH</t>
+        </is>
+      </c>
       <c r="C114" t="n">
         <v>13686</v>
       </c>
@@ -12818,7 +13270,11 @@
       <c r="A115" t="n">
         <v>7</v>
       </c>
-      <c r="B115" t="inlineStr"/>
+      <c r="B115" t="inlineStr">
+        <is>
+          <t>BREATH</t>
+        </is>
+      </c>
       <c r="C115" t="n">
         <v>13786</v>
       </c>
@@ -12926,7 +13382,11 @@
       <c r="A116" t="n">
         <v>7</v>
       </c>
-      <c r="B116" t="inlineStr"/>
+      <c r="B116" t="inlineStr">
+        <is>
+          <t>BREATH</t>
+        </is>
+      </c>
       <c r="C116" t="n">
         <v>13886</v>
       </c>
@@ -13034,7 +13494,11 @@
       <c r="A117" t="n">
         <v>7</v>
       </c>
-      <c r="B117" t="inlineStr"/>
+      <c r="B117" t="inlineStr">
+        <is>
+          <t>BREATH</t>
+        </is>
+      </c>
       <c r="C117" t="n">
         <v>13986</v>
       </c>
@@ -13142,7 +13606,11 @@
       <c r="A118" t="n">
         <v>7</v>
       </c>
-      <c r="B118" t="inlineStr"/>
+      <c r="B118" t="inlineStr">
+        <is>
+          <t>BREATH</t>
+        </is>
+      </c>
       <c r="C118" t="n">
         <v>14086</v>
       </c>
@@ -13250,7 +13718,11 @@
       <c r="A119" t="n">
         <v>7</v>
       </c>
-      <c r="B119" t="inlineStr"/>
+      <c r="B119" t="inlineStr">
+        <is>
+          <t>BREATH</t>
+        </is>
+      </c>
       <c r="C119" t="n">
         <v>14186</v>
       </c>
@@ -13358,7 +13830,11 @@
       <c r="A120" t="n">
         <v>7</v>
       </c>
-      <c r="B120" t="inlineStr"/>
+      <c r="B120" t="inlineStr">
+        <is>
+          <t>BREATH</t>
+        </is>
+      </c>
       <c r="C120" t="n">
         <v>14286</v>
       </c>
@@ -13466,7 +13942,11 @@
       <c r="A121" t="n">
         <v>7</v>
       </c>
-      <c r="B121" t="inlineStr"/>
+      <c r="B121" t="inlineStr">
+        <is>
+          <t>BREATH</t>
+        </is>
+      </c>
       <c r="C121" t="n">
         <v>14386</v>
       </c>
@@ -13574,7 +14054,11 @@
       <c r="A122" t="n">
         <v>7</v>
       </c>
-      <c r="B122" t="inlineStr"/>
+      <c r="B122" t="inlineStr">
+        <is>
+          <t>BREATH</t>
+        </is>
+      </c>
       <c r="C122" t="n">
         <v>14486</v>
       </c>
@@ -13682,7 +14166,11 @@
       <c r="A123" t="n">
         <v>7</v>
       </c>
-      <c r="B123" t="inlineStr"/>
+      <c r="B123" t="inlineStr">
+        <is>
+          <t>BREATH</t>
+        </is>
+      </c>
       <c r="C123" t="n">
         <v>14586</v>
       </c>
@@ -13790,7 +14278,11 @@
       <c r="A124" t="n">
         <v>7</v>
       </c>
-      <c r="B124" t="inlineStr"/>
+      <c r="B124" t="inlineStr">
+        <is>
+          <t>BREATH</t>
+        </is>
+      </c>
       <c r="C124" t="n">
         <v>14686</v>
       </c>
@@ -13898,7 +14390,11 @@
       <c r="A125" t="n">
         <v>7</v>
       </c>
-      <c r="B125" t="inlineStr"/>
+      <c r="B125" t="inlineStr">
+        <is>
+          <t>BREATH</t>
+        </is>
+      </c>
       <c r="C125" t="n">
         <v>14786</v>
       </c>
@@ -14006,7 +14502,11 @@
       <c r="A126" t="n">
         <v>7</v>
       </c>
-      <c r="B126" t="inlineStr"/>
+      <c r="B126" t="inlineStr">
+        <is>
+          <t>BREATH</t>
+        </is>
+      </c>
       <c r="C126" t="n">
         <v>14886</v>
       </c>
@@ -14114,7 +14614,11 @@
       <c r="A127" t="n">
         <v>7</v>
       </c>
-      <c r="B127" t="inlineStr"/>
+      <c r="B127" t="inlineStr">
+        <is>
+          <t>BREATH</t>
+        </is>
+      </c>
       <c r="C127" t="n">
         <v>14986</v>
       </c>
@@ -14222,7 +14726,11 @@
       <c r="A128" t="n">
         <v>7</v>
       </c>
-      <c r="B128" t="inlineStr"/>
+      <c r="B128" t="inlineStr">
+        <is>
+          <t>BREATH</t>
+        </is>
+      </c>
       <c r="C128" t="n">
         <v>15086</v>
       </c>
@@ -14330,7 +14838,11 @@
       <c r="A129" t="n">
         <v>7</v>
       </c>
-      <c r="B129" t="inlineStr"/>
+      <c r="B129" t="inlineStr">
+        <is>
+          <t>BREATH</t>
+        </is>
+      </c>
       <c r="C129" t="n">
         <v>15186</v>
       </c>
@@ -14438,7 +14950,11 @@
       <c r="A130" t="n">
         <v>7</v>
       </c>
-      <c r="B130" t="inlineStr"/>
+      <c r="B130" t="inlineStr">
+        <is>
+          <t>BREATH</t>
+        </is>
+      </c>
       <c r="C130" t="n">
         <v>15286</v>
       </c>
@@ -14546,7 +15062,11 @@
       <c r="A131" t="n">
         <v>7</v>
       </c>
-      <c r="B131" t="inlineStr"/>
+      <c r="B131" t="inlineStr">
+        <is>
+          <t>BREATH</t>
+        </is>
+      </c>
       <c r="C131" t="n">
         <v>15386</v>
       </c>
@@ -14654,7 +15174,11 @@
       <c r="A132" t="n">
         <v>7</v>
       </c>
-      <c r="B132" t="inlineStr"/>
+      <c r="B132" t="inlineStr">
+        <is>
+          <t>BREATH</t>
+        </is>
+      </c>
       <c r="C132" t="n">
         <v>15486</v>
       </c>
@@ -14762,7 +15286,11 @@
       <c r="A133" t="n">
         <v>7</v>
       </c>
-      <c r="B133" t="inlineStr"/>
+      <c r="B133" t="inlineStr">
+        <is>
+          <t>BREATH</t>
+        </is>
+      </c>
       <c r="C133" t="n">
         <v>15586</v>
       </c>
@@ -14870,7 +15398,11 @@
       <c r="A134" t="n">
         <v>7</v>
       </c>
-      <c r="B134" t="inlineStr"/>
+      <c r="B134" t="inlineStr">
+        <is>
+          <t>BREATH</t>
+        </is>
+      </c>
       <c r="C134" t="n">
         <v>15686</v>
       </c>
@@ -14978,7 +15510,11 @@
       <c r="A135" t="n">
         <v>7</v>
       </c>
-      <c r="B135" t="inlineStr"/>
+      <c r="B135" t="inlineStr">
+        <is>
+          <t>BREATH</t>
+        </is>
+      </c>
       <c r="C135" t="n">
         <v>15786</v>
       </c>
@@ -15086,7 +15622,11 @@
       <c r="A136" t="n">
         <v>7</v>
       </c>
-      <c r="B136" t="inlineStr"/>
+      <c r="B136" t="inlineStr">
+        <is>
+          <t>BREATH</t>
+        </is>
+      </c>
       <c r="C136" t="n">
         <v>15886</v>
       </c>
@@ -15194,7 +15734,11 @@
       <c r="A137" t="n">
         <v>7</v>
       </c>
-      <c r="B137" t="inlineStr"/>
+      <c r="B137" t="inlineStr">
+        <is>
+          <t>BREATH</t>
+        </is>
+      </c>
       <c r="C137" t="n">
         <v>15986</v>
       </c>
@@ -15302,7 +15846,11 @@
       <c r="A138" t="n">
         <v>7</v>
       </c>
-      <c r="B138" t="inlineStr"/>
+      <c r="B138" t="inlineStr">
+        <is>
+          <t>BREATH</t>
+        </is>
+      </c>
       <c r="C138" t="n">
         <v>16086</v>
       </c>
@@ -15410,7 +15958,11 @@
       <c r="A139" t="n">
         <v>7</v>
       </c>
-      <c r="B139" t="inlineStr"/>
+      <c r="B139" t="inlineStr">
+        <is>
+          <t>BREATH</t>
+        </is>
+      </c>
       <c r="C139" t="n">
         <v>16186</v>
       </c>
@@ -15518,7 +16070,11 @@
       <c r="A140" t="n">
         <v>7</v>
       </c>
-      <c r="B140" t="inlineStr"/>
+      <c r="B140" t="inlineStr">
+        <is>
+          <t>BREATH</t>
+        </is>
+      </c>
       <c r="C140" t="n">
         <v>16286</v>
       </c>
@@ -15626,7 +16182,11 @@
       <c r="A141" t="n">
         <v>7</v>
       </c>
-      <c r="B141" t="inlineStr"/>
+      <c r="B141" t="inlineStr">
+        <is>
+          <t>BREATH</t>
+        </is>
+      </c>
       <c r="C141" t="n">
         <v>16386</v>
       </c>
@@ -15734,7 +16294,11 @@
       <c r="A142" t="n">
         <v>7</v>
       </c>
-      <c r="B142" t="inlineStr"/>
+      <c r="B142" t="inlineStr">
+        <is>
+          <t>BREATH</t>
+        </is>
+      </c>
       <c r="C142" t="n">
         <v>16486</v>
       </c>
@@ -15842,7 +16406,11 @@
       <c r="A143" t="n">
         <v>7</v>
       </c>
-      <c r="B143" t="inlineStr"/>
+      <c r="B143" t="inlineStr">
+        <is>
+          <t>BREATH</t>
+        </is>
+      </c>
       <c r="C143" t="n">
         <v>16586</v>
       </c>
@@ -15950,7 +16518,11 @@
       <c r="A144" t="n">
         <v>7</v>
       </c>
-      <c r="B144" t="inlineStr"/>
+      <c r="B144" t="inlineStr">
+        <is>
+          <t>BREATH</t>
+        </is>
+      </c>
       <c r="C144" t="n">
         <v>16686</v>
       </c>
@@ -16058,7 +16630,11 @@
       <c r="A145" t="n">
         <v>7</v>
       </c>
-      <c r="B145" t="inlineStr"/>
+      <c r="B145" t="inlineStr">
+        <is>
+          <t>BREATH</t>
+        </is>
+      </c>
       <c r="C145" t="n">
         <v>16786</v>
       </c>
@@ -16166,7 +16742,11 @@
       <c r="A146" t="n">
         <v>7</v>
       </c>
-      <c r="B146" t="inlineStr"/>
+      <c r="B146" t="inlineStr">
+        <is>
+          <t>BREATH</t>
+        </is>
+      </c>
       <c r="C146" t="n">
         <v>16886</v>
       </c>
@@ -16274,7 +16854,11 @@
       <c r="A147" t="n">
         <v>7</v>
       </c>
-      <c r="B147" t="inlineStr"/>
+      <c r="B147" t="inlineStr">
+        <is>
+          <t>BREATH</t>
+        </is>
+      </c>
       <c r="C147" t="n">
         <v>16986</v>
       </c>
@@ -16382,7 +16966,11 @@
       <c r="A148" t="n">
         <v>7</v>
       </c>
-      <c r="B148" t="inlineStr"/>
+      <c r="B148" t="inlineStr">
+        <is>
+          <t>BREATH</t>
+        </is>
+      </c>
       <c r="C148" t="n">
         <v>17086</v>
       </c>
@@ -16490,7 +17078,11 @@
       <c r="A149" t="n">
         <v>7</v>
       </c>
-      <c r="B149" t="inlineStr"/>
+      <c r="B149" t="inlineStr">
+        <is>
+          <t>BREATH</t>
+        </is>
+      </c>
       <c r="C149" t="n">
         <v>17186</v>
       </c>
@@ -16598,7 +17190,11 @@
       <c r="A150" t="n">
         <v>7</v>
       </c>
-      <c r="B150" t="inlineStr"/>
+      <c r="B150" t="inlineStr">
+        <is>
+          <t>BREATH</t>
+        </is>
+      </c>
       <c r="C150" t="n">
         <v>17286</v>
       </c>
@@ -16706,7 +17302,11 @@
       <c r="A151" t="n">
         <v>7</v>
       </c>
-      <c r="B151" t="inlineStr"/>
+      <c r="B151" t="inlineStr">
+        <is>
+          <t>BREATH</t>
+        </is>
+      </c>
       <c r="C151" t="n">
         <v>17386</v>
       </c>
@@ -16814,7 +17414,11 @@
       <c r="A152" t="n">
         <v>7</v>
       </c>
-      <c r="B152" t="inlineStr"/>
+      <c r="B152" t="inlineStr">
+        <is>
+          <t>BREATH</t>
+        </is>
+      </c>
       <c r="C152" t="n">
         <v>17486</v>
       </c>
@@ -16922,7 +17526,11 @@
       <c r="A153" t="n">
         <v>7</v>
       </c>
-      <c r="B153" t="inlineStr"/>
+      <c r="B153" t="inlineStr">
+        <is>
+          <t>BREATH</t>
+        </is>
+      </c>
       <c r="C153" t="n">
         <v>17586</v>
       </c>
@@ -17030,7 +17638,11 @@
       <c r="A154" t="n">
         <v>7</v>
       </c>
-      <c r="B154" t="inlineStr"/>
+      <c r="B154" t="inlineStr">
+        <is>
+          <t>BREATH</t>
+        </is>
+      </c>
       <c r="C154" t="n">
         <v>17686</v>
       </c>
@@ -17138,7 +17750,11 @@
       <c r="A155" t="n">
         <v>7</v>
       </c>
-      <c r="B155" t="inlineStr"/>
+      <c r="B155" t="inlineStr">
+        <is>
+          <t>BREATH</t>
+        </is>
+      </c>
       <c r="C155" t="n">
         <v>17786</v>
       </c>
@@ -17246,7 +17862,11 @@
       <c r="A156" t="n">
         <v>7</v>
       </c>
-      <c r="B156" t="inlineStr"/>
+      <c r="B156" t="inlineStr">
+        <is>
+          <t>BREATH</t>
+        </is>
+      </c>
       <c r="C156" t="n">
         <v>17886</v>
       </c>
@@ -17354,7 +17974,11 @@
       <c r="A157" t="n">
         <v>7</v>
       </c>
-      <c r="B157" t="inlineStr"/>
+      <c r="B157" t="inlineStr">
+        <is>
+          <t>BREATH</t>
+        </is>
+      </c>
       <c r="C157" t="n">
         <v>17986</v>
       </c>
@@ -17462,7 +18086,11 @@
       <c r="A158" t="n">
         <v>7</v>
       </c>
-      <c r="B158" t="inlineStr"/>
+      <c r="B158" t="inlineStr">
+        <is>
+          <t>BREATH</t>
+        </is>
+      </c>
       <c r="C158" t="n">
         <v>18086</v>
       </c>
@@ -17570,7 +18198,11 @@
       <c r="A159" t="n">
         <v>8</v>
       </c>
-      <c r="B159" t="inlineStr"/>
+      <c r="B159" t="inlineStr">
+        <is>
+          <t>CLOSE</t>
+        </is>
+      </c>
       <c r="C159" t="n">
         <v>18096</v>
       </c>
@@ -17678,7 +18310,11 @@
       <c r="A160" t="n">
         <v>9</v>
       </c>
-      <c r="B160" t="inlineStr"/>
+      <c r="B160" t="inlineStr">
+        <is>
+          <t>CHANGE</t>
+        </is>
+      </c>
       <c r="C160" t="n">
         <v>19109</v>
       </c>
@@ -17786,7 +18422,11 @@
       <c r="A161" t="n">
         <v>10</v>
       </c>
-      <c r="B161" t="inlineStr"/>
+      <c r="B161" t="inlineStr">
+        <is>
+          <t>OPEN</t>
+        </is>
+      </c>
       <c r="C161" t="n">
         <v>19119</v>
       </c>
@@ -17894,7 +18534,11 @@
       <c r="A162" t="n">
         <v>11</v>
       </c>
-      <c r="B162" t="inlineStr"/>
+      <c r="B162" t="inlineStr">
+        <is>
+          <t>POST</t>
+        </is>
+      </c>
       <c r="C162" t="n">
         <v>20131</v>
       </c>
@@ -18002,7 +18646,11 @@
       <c r="A163" t="n">
         <v>11</v>
       </c>
-      <c r="B163" t="inlineStr"/>
+      <c r="B163" t="inlineStr">
+        <is>
+          <t>POST</t>
+        </is>
+      </c>
       <c r="C163" t="n">
         <v>20231</v>
       </c>
@@ -18110,7 +18758,11 @@
       <c r="A164" t="n">
         <v>11</v>
       </c>
-      <c r="B164" t="inlineStr"/>
+      <c r="B164" t="inlineStr">
+        <is>
+          <t>POST</t>
+        </is>
+      </c>
       <c r="C164" t="n">
         <v>20331</v>
       </c>
@@ -18218,7 +18870,11 @@
       <c r="A165" t="n">
         <v>11</v>
       </c>
-      <c r="B165" t="inlineStr"/>
+      <c r="B165" t="inlineStr">
+        <is>
+          <t>POST</t>
+        </is>
+      </c>
       <c r="C165" t="n">
         <v>20431</v>
       </c>
@@ -18326,7 +18982,11 @@
       <c r="A166" t="n">
         <v>11</v>
       </c>
-      <c r="B166" t="inlineStr"/>
+      <c r="B166" t="inlineStr">
+        <is>
+          <t>POST</t>
+        </is>
+      </c>
       <c r="C166" t="n">
         <v>20531</v>
       </c>
@@ -18434,7 +19094,11 @@
       <c r="A167" t="n">
         <v>11</v>
       </c>
-      <c r="B167" t="inlineStr"/>
+      <c r="B167" t="inlineStr">
+        <is>
+          <t>POST</t>
+        </is>
+      </c>
       <c r="C167" t="n">
         <v>20631</v>
       </c>
@@ -18542,7 +19206,11 @@
       <c r="A168" t="n">
         <v>11</v>
       </c>
-      <c r="B168" t="inlineStr"/>
+      <c r="B168" t="inlineStr">
+        <is>
+          <t>POST</t>
+        </is>
+      </c>
       <c r="C168" t="n">
         <v>20731</v>
       </c>
@@ -18650,7 +19318,11 @@
       <c r="A169" t="n">
         <v>11</v>
       </c>
-      <c r="B169" t="inlineStr"/>
+      <c r="B169" t="inlineStr">
+        <is>
+          <t>POST</t>
+        </is>
+      </c>
       <c r="C169" t="n">
         <v>20831</v>
       </c>
@@ -18758,7 +19430,11 @@
       <c r="A170" t="n">
         <v>11</v>
       </c>
-      <c r="B170" t="inlineStr"/>
+      <c r="B170" t="inlineStr">
+        <is>
+          <t>POST</t>
+        </is>
+      </c>
       <c r="C170" t="n">
         <v>20931</v>
       </c>
@@ -18866,7 +19542,11 @@
       <c r="A171" t="n">
         <v>11</v>
       </c>
-      <c r="B171" t="inlineStr"/>
+      <c r="B171" t="inlineStr">
+        <is>
+          <t>POST</t>
+        </is>
+      </c>
       <c r="C171" t="n">
         <v>21031</v>
       </c>
@@ -18974,7 +19654,11 @@
       <c r="A172" t="n">
         <v>11</v>
       </c>
-      <c r="B172" t="inlineStr"/>
+      <c r="B172" t="inlineStr">
+        <is>
+          <t>POST</t>
+        </is>
+      </c>
       <c r="C172" t="n">
         <v>21131</v>
       </c>
@@ -19082,7 +19766,11 @@
       <c r="A173" t="n">
         <v>11</v>
       </c>
-      <c r="B173" t="inlineStr"/>
+      <c r="B173" t="inlineStr">
+        <is>
+          <t>POST</t>
+        </is>
+      </c>
       <c r="C173" t="n">
         <v>21231</v>
       </c>
@@ -19190,7 +19878,11 @@
       <c r="A174" t="n">
         <v>11</v>
       </c>
-      <c r="B174" t="inlineStr"/>
+      <c r="B174" t="inlineStr">
+        <is>
+          <t>POST</t>
+        </is>
+      </c>
       <c r="C174" t="n">
         <v>21331</v>
       </c>
@@ -19298,7 +19990,11 @@
       <c r="A175" t="n">
         <v>11</v>
       </c>
-      <c r="B175" t="inlineStr"/>
+      <c r="B175" t="inlineStr">
+        <is>
+          <t>POST</t>
+        </is>
+      </c>
       <c r="C175" t="n">
         <v>21431</v>
       </c>
@@ -19406,7 +20102,11 @@
       <c r="A176" t="n">
         <v>11</v>
       </c>
-      <c r="B176" t="inlineStr"/>
+      <c r="B176" t="inlineStr">
+        <is>
+          <t>POST</t>
+        </is>
+      </c>
       <c r="C176" t="n">
         <v>21531</v>
       </c>
@@ -19514,7 +20214,11 @@
       <c r="A177" t="n">
         <v>11</v>
       </c>
-      <c r="B177" t="inlineStr"/>
+      <c r="B177" t="inlineStr">
+        <is>
+          <t>POST</t>
+        </is>
+      </c>
       <c r="C177" t="n">
         <v>21631</v>
       </c>
@@ -19622,7 +20326,11 @@
       <c r="A178" t="n">
         <v>11</v>
       </c>
-      <c r="B178" t="inlineStr"/>
+      <c r="B178" t="inlineStr">
+        <is>
+          <t>POST</t>
+        </is>
+      </c>
       <c r="C178" t="n">
         <v>21731</v>
       </c>
@@ -19730,7 +20438,11 @@
       <c r="A179" t="n">
         <v>11</v>
       </c>
-      <c r="B179" t="inlineStr"/>
+      <c r="B179" t="inlineStr">
+        <is>
+          <t>POST</t>
+        </is>
+      </c>
       <c r="C179" t="n">
         <v>21831</v>
       </c>
@@ -19838,7 +20550,11 @@
       <c r="A180" t="n">
         <v>11</v>
       </c>
-      <c r="B180" t="inlineStr"/>
+      <c r="B180" t="inlineStr">
+        <is>
+          <t>POST</t>
+        </is>
+      </c>
       <c r="C180" t="n">
         <v>21931</v>
       </c>
@@ -19946,7 +20662,11 @@
       <c r="A181" t="n">
         <v>11</v>
       </c>
-      <c r="B181" t="inlineStr"/>
+      <c r="B181" t="inlineStr">
+        <is>
+          <t>POST</t>
+        </is>
+      </c>
       <c r="C181" t="n">
         <v>22031</v>
       </c>
@@ -20054,7 +20774,11 @@
       <c r="A182" t="n">
         <v>11</v>
       </c>
-      <c r="B182" t="inlineStr"/>
+      <c r="B182" t="inlineStr">
+        <is>
+          <t>POST</t>
+        </is>
+      </c>
       <c r="C182" t="n">
         <v>22131</v>
       </c>
@@ -20162,7 +20886,11 @@
       <c r="A183" t="n">
         <v>11</v>
       </c>
-      <c r="B183" t="inlineStr"/>
+      <c r="B183" t="inlineStr">
+        <is>
+          <t>POST</t>
+        </is>
+      </c>
       <c r="C183" t="n">
         <v>22231</v>
       </c>
@@ -20270,7 +20998,11 @@
       <c r="A184" t="n">
         <v>11</v>
       </c>
-      <c r="B184" t="inlineStr"/>
+      <c r="B184" t="inlineStr">
+        <is>
+          <t>POST</t>
+        </is>
+      </c>
       <c r="C184" t="n">
         <v>22331</v>
       </c>
@@ -20378,7 +21110,11 @@
       <c r="A185" t="n">
         <v>11</v>
       </c>
-      <c r="B185" t="inlineStr"/>
+      <c r="B185" t="inlineStr">
+        <is>
+          <t>POST</t>
+        </is>
+      </c>
       <c r="C185" t="n">
         <v>22431</v>
       </c>
@@ -20486,7 +21222,11 @@
       <c r="A186" t="n">
         <v>11</v>
       </c>
-      <c r="B186" t="inlineStr"/>
+      <c r="B186" t="inlineStr">
+        <is>
+          <t>POST</t>
+        </is>
+      </c>
       <c r="C186" t="n">
         <v>22531</v>
       </c>
@@ -20594,7 +21334,11 @@
       <c r="A187" t="n">
         <v>11</v>
       </c>
-      <c r="B187" t="inlineStr"/>
+      <c r="B187" t="inlineStr">
+        <is>
+          <t>POST</t>
+        </is>
+      </c>
       <c r="C187" t="n">
         <v>22631</v>
       </c>
@@ -20702,7 +21446,11 @@
       <c r="A188" t="n">
         <v>11</v>
       </c>
-      <c r="B188" t="inlineStr"/>
+      <c r="B188" t="inlineStr">
+        <is>
+          <t>POST</t>
+        </is>
+      </c>
       <c r="C188" t="n">
         <v>22731</v>
       </c>
@@ -20810,7 +21558,11 @@
       <c r="A189" t="n">
         <v>11</v>
       </c>
-      <c r="B189" t="inlineStr"/>
+      <c r="B189" t="inlineStr">
+        <is>
+          <t>POST</t>
+        </is>
+      </c>
       <c r="C189" t="n">
         <v>22831</v>
       </c>
@@ -20918,7 +21670,11 @@
       <c r="A190" t="n">
         <v>11</v>
       </c>
-      <c r="B190" t="inlineStr"/>
+      <c r="B190" t="inlineStr">
+        <is>
+          <t>POST</t>
+        </is>
+      </c>
       <c r="C190" t="n">
         <v>22931</v>
       </c>
@@ -21026,7 +21782,11 @@
       <c r="A191" t="n">
         <v>11</v>
       </c>
-      <c r="B191" t="inlineStr"/>
+      <c r="B191" t="inlineStr">
+        <is>
+          <t>POST</t>
+        </is>
+      </c>
       <c r="C191" t="n">
         <v>23031</v>
       </c>
@@ -21134,7 +21894,11 @@
       <c r="A192" t="n">
         <v>11</v>
       </c>
-      <c r="B192" t="inlineStr"/>
+      <c r="B192" t="inlineStr">
+        <is>
+          <t>POST</t>
+        </is>
+      </c>
       <c r="C192" t="n">
         <v>23131</v>
       </c>
@@ -21242,7 +22006,11 @@
       <c r="A193" t="n">
         <v>11</v>
       </c>
-      <c r="B193" t="inlineStr"/>
+      <c r="B193" t="inlineStr">
+        <is>
+          <t>POST</t>
+        </is>
+      </c>
       <c r="C193" t="n">
         <v>23231</v>
       </c>
@@ -21350,7 +22118,11 @@
       <c r="A194" t="n">
         <v>11</v>
       </c>
-      <c r="B194" t="inlineStr"/>
+      <c r="B194" t="inlineStr">
+        <is>
+          <t>POST</t>
+        </is>
+      </c>
       <c r="C194" t="n">
         <v>23331</v>
       </c>
@@ -21458,7 +22230,11 @@
       <c r="A195" t="n">
         <v>11</v>
       </c>
-      <c r="B195" t="inlineStr"/>
+      <c r="B195" t="inlineStr">
+        <is>
+          <t>POST</t>
+        </is>
+      </c>
       <c r="C195" t="n">
         <v>23431</v>
       </c>
@@ -21566,7 +22342,11 @@
       <c r="A196" t="n">
         <v>11</v>
       </c>
-      <c r="B196" t="inlineStr"/>
+      <c r="B196" t="inlineStr">
+        <is>
+          <t>POST</t>
+        </is>
+      </c>
       <c r="C196" t="n">
         <v>23531</v>
       </c>
@@ -21674,7 +22454,11 @@
       <c r="A197" t="n">
         <v>11</v>
       </c>
-      <c r="B197" t="inlineStr"/>
+      <c r="B197" t="inlineStr">
+        <is>
+          <t>POST</t>
+        </is>
+      </c>
       <c r="C197" t="n">
         <v>23631</v>
       </c>
@@ -21782,7 +22566,11 @@
       <c r="A198" t="n">
         <v>11</v>
       </c>
-      <c r="B198" t="inlineStr"/>
+      <c r="B198" t="inlineStr">
+        <is>
+          <t>POST</t>
+        </is>
+      </c>
       <c r="C198" t="n">
         <v>23731</v>
       </c>
@@ -21890,7 +22678,11 @@
       <c r="A199" t="n">
         <v>11</v>
       </c>
-      <c r="B199" t="inlineStr"/>
+      <c r="B199" t="inlineStr">
+        <is>
+          <t>POST</t>
+        </is>
+      </c>
       <c r="C199" t="n">
         <v>23831</v>
       </c>
@@ -21998,7 +22790,11 @@
       <c r="A200" t="n">
         <v>11</v>
       </c>
-      <c r="B200" t="inlineStr"/>
+      <c r="B200" t="inlineStr">
+        <is>
+          <t>POST</t>
+        </is>
+      </c>
       <c r="C200" t="n">
         <v>23931</v>
       </c>
@@ -22106,7 +22902,11 @@
       <c r="A201" t="n">
         <v>11</v>
       </c>
-      <c r="B201" t="inlineStr"/>
+      <c r="B201" t="inlineStr">
+        <is>
+          <t>POST</t>
+        </is>
+      </c>
       <c r="C201" t="n">
         <v>24031</v>
       </c>
@@ -22214,7 +23014,11 @@
       <c r="A202" t="n">
         <v>11</v>
       </c>
-      <c r="B202" t="inlineStr"/>
+      <c r="B202" t="inlineStr">
+        <is>
+          <t>POST</t>
+        </is>
+      </c>
       <c r="C202" t="n">
         <v>24131</v>
       </c>
@@ -22322,7 +23126,11 @@
       <c r="A203" t="n">
         <v>11</v>
       </c>
-      <c r="B203" t="inlineStr"/>
+      <c r="B203" t="inlineStr">
+        <is>
+          <t>POST</t>
+        </is>
+      </c>
       <c r="C203" t="n">
         <v>24231</v>
       </c>
@@ -22430,7 +23238,11 @@
       <c r="A204" t="n">
         <v>11</v>
       </c>
-      <c r="B204" t="inlineStr"/>
+      <c r="B204" t="inlineStr">
+        <is>
+          <t>POST</t>
+        </is>
+      </c>
       <c r="C204" t="n">
         <v>24331</v>
       </c>
@@ -22538,7 +23350,11 @@
       <c r="A205" t="n">
         <v>11</v>
       </c>
-      <c r="B205" t="inlineStr"/>
+      <c r="B205" t="inlineStr">
+        <is>
+          <t>POST</t>
+        </is>
+      </c>
       <c r="C205" t="n">
         <v>24431</v>
       </c>
@@ -22646,7 +23462,11 @@
       <c r="A206" t="n">
         <v>11</v>
       </c>
-      <c r="B206" t="inlineStr"/>
+      <c r="B206" t="inlineStr">
+        <is>
+          <t>POST</t>
+        </is>
+      </c>
       <c r="C206" t="n">
         <v>24531</v>
       </c>
@@ -22754,7 +23574,11 @@
       <c r="A207" t="n">
         <v>11</v>
       </c>
-      <c r="B207" t="inlineStr"/>
+      <c r="B207" t="inlineStr">
+        <is>
+          <t>POST</t>
+        </is>
+      </c>
       <c r="C207" t="n">
         <v>24631</v>
       </c>
@@ -22862,7 +23686,11 @@
       <c r="A208" t="n">
         <v>11</v>
       </c>
-      <c r="B208" t="inlineStr"/>
+      <c r="B208" t="inlineStr">
+        <is>
+          <t>POST</t>
+        </is>
+      </c>
       <c r="C208" t="n">
         <v>24731</v>
       </c>
@@ -22970,7 +23798,11 @@
       <c r="A209" t="n">
         <v>11</v>
       </c>
-      <c r="B209" t="inlineStr"/>
+      <c r="B209" t="inlineStr">
+        <is>
+          <t>POST</t>
+        </is>
+      </c>
       <c r="C209" t="n">
         <v>24831</v>
       </c>
@@ -23078,7 +23910,11 @@
       <c r="A210" t="n">
         <v>11</v>
       </c>
-      <c r="B210" t="inlineStr"/>
+      <c r="B210" t="inlineStr">
+        <is>
+          <t>POST</t>
+        </is>
+      </c>
       <c r="C210" t="n">
         <v>24931</v>
       </c>
@@ -23186,7 +24022,11 @@
       <c r="A211" t="n">
         <v>11</v>
       </c>
-      <c r="B211" t="inlineStr"/>
+      <c r="B211" t="inlineStr">
+        <is>
+          <t>POST</t>
+        </is>
+      </c>
       <c r="C211" t="n">
         <v>25031</v>
       </c>
@@ -23294,7 +24134,11 @@
       <c r="A212" t="n">
         <v>11</v>
       </c>
-      <c r="B212" t="inlineStr"/>
+      <c r="B212" t="inlineStr">
+        <is>
+          <t>POST</t>
+        </is>
+      </c>
       <c r="C212" t="n">
         <v>25131</v>
       </c>
@@ -23402,7 +24246,11 @@
       <c r="A213" t="n">
         <v>11</v>
       </c>
-      <c r="B213" t="inlineStr"/>
+      <c r="B213" t="inlineStr">
+        <is>
+          <t>POST</t>
+        </is>
+      </c>
       <c r="C213" t="n">
         <v>25231</v>
       </c>
@@ -23510,7 +24358,11 @@
       <c r="A214" t="n">
         <v>11</v>
       </c>
-      <c r="B214" t="inlineStr"/>
+      <c r="B214" t="inlineStr">
+        <is>
+          <t>POST</t>
+        </is>
+      </c>
       <c r="C214" t="n">
         <v>25331</v>
       </c>
@@ -23618,7 +24470,11 @@
       <c r="A215" t="n">
         <v>11</v>
       </c>
-      <c r="B215" t="inlineStr"/>
+      <c r="B215" t="inlineStr">
+        <is>
+          <t>POST</t>
+        </is>
+      </c>
       <c r="C215" t="n">
         <v>25431</v>
       </c>
@@ -23726,7 +24582,11 @@
       <c r="A216" t="n">
         <v>11</v>
       </c>
-      <c r="B216" t="inlineStr"/>
+      <c r="B216" t="inlineStr">
+        <is>
+          <t>POST</t>
+        </is>
+      </c>
       <c r="C216" t="n">
         <v>25531</v>
       </c>
@@ -23834,7 +24694,11 @@
       <c r="A217" t="n">
         <v>11</v>
       </c>
-      <c r="B217" t="inlineStr"/>
+      <c r="B217" t="inlineStr">
+        <is>
+          <t>POST</t>
+        </is>
+      </c>
       <c r="C217" t="n">
         <v>25631</v>
       </c>
@@ -23942,7 +24806,11 @@
       <c r="A218" t="n">
         <v>11</v>
       </c>
-      <c r="B218" t="inlineStr"/>
+      <c r="B218" t="inlineStr">
+        <is>
+          <t>POST</t>
+        </is>
+      </c>
       <c r="C218" t="n">
         <v>25731</v>
       </c>
@@ -24050,7 +24918,11 @@
       <c r="A219" t="n">
         <v>11</v>
       </c>
-      <c r="B219" t="inlineStr"/>
+      <c r="B219" t="inlineStr">
+        <is>
+          <t>POST</t>
+        </is>
+      </c>
       <c r="C219" t="n">
         <v>25831</v>
       </c>
@@ -24158,7 +25030,11 @@
       <c r="A220" t="n">
         <v>11</v>
       </c>
-      <c r="B220" t="inlineStr"/>
+      <c r="B220" t="inlineStr">
+        <is>
+          <t>POST</t>
+        </is>
+      </c>
       <c r="C220" t="n">
         <v>25931</v>
       </c>
@@ -24266,7 +25142,11 @@
       <c r="A221" t="n">
         <v>11</v>
       </c>
-      <c r="B221" t="inlineStr"/>
+      <c r="B221" t="inlineStr">
+        <is>
+          <t>POST</t>
+        </is>
+      </c>
       <c r="C221" t="n">
         <v>26031</v>
       </c>
@@ -24374,7 +25254,11 @@
       <c r="A222" t="n">
         <v>11</v>
       </c>
-      <c r="B222" t="inlineStr"/>
+      <c r="B222" t="inlineStr">
+        <is>
+          <t>POST</t>
+        </is>
+      </c>
       <c r="C222" t="n">
         <v>26131</v>
       </c>
@@ -24482,7 +25366,11 @@
       <c r="A223" t="n">
         <v>11</v>
       </c>
-      <c r="B223" t="inlineStr"/>
+      <c r="B223" t="inlineStr">
+        <is>
+          <t>POST</t>
+        </is>
+      </c>
       <c r="C223" t="n">
         <v>26231</v>
       </c>
@@ -24590,7 +25478,11 @@
       <c r="A224" t="n">
         <v>11</v>
       </c>
-      <c r="B224" t="inlineStr"/>
+      <c r="B224" t="inlineStr">
+        <is>
+          <t>POST</t>
+        </is>
+      </c>
       <c r="C224" t="n">
         <v>26331</v>
       </c>
@@ -24698,7 +25590,11 @@
       <c r="A225" t="n">
         <v>11</v>
       </c>
-      <c r="B225" t="inlineStr"/>
+      <c r="B225" t="inlineStr">
+        <is>
+          <t>POST</t>
+        </is>
+      </c>
       <c r="C225" t="n">
         <v>26431</v>
       </c>
@@ -24806,7 +25702,11 @@
       <c r="A226" t="n">
         <v>11</v>
       </c>
-      <c r="B226" t="inlineStr"/>
+      <c r="B226" t="inlineStr">
+        <is>
+          <t>POST</t>
+        </is>
+      </c>
       <c r="C226" t="n">
         <v>26531</v>
       </c>
@@ -24914,7 +25814,11 @@
       <c r="A227" t="n">
         <v>11</v>
       </c>
-      <c r="B227" t="inlineStr"/>
+      <c r="B227" t="inlineStr">
+        <is>
+          <t>POST</t>
+        </is>
+      </c>
       <c r="C227" t="n">
         <v>26631</v>
       </c>
@@ -25022,7 +25926,11 @@
       <c r="A228" t="n">
         <v>11</v>
       </c>
-      <c r="B228" t="inlineStr"/>
+      <c r="B228" t="inlineStr">
+        <is>
+          <t>POST</t>
+        </is>
+      </c>
       <c r="C228" t="n">
         <v>26731</v>
       </c>
@@ -25130,7 +26038,11 @@
       <c r="A229" t="n">
         <v>11</v>
       </c>
-      <c r="B229" t="inlineStr"/>
+      <c r="B229" t="inlineStr">
+        <is>
+          <t>POST</t>
+        </is>
+      </c>
       <c r="C229" t="n">
         <v>26831</v>
       </c>
@@ -25238,7 +26150,11 @@
       <c r="A230" t="n">
         <v>11</v>
       </c>
-      <c r="B230" t="inlineStr"/>
+      <c r="B230" t="inlineStr">
+        <is>
+          <t>POST</t>
+        </is>
+      </c>
       <c r="C230" t="n">
         <v>26931</v>
       </c>
@@ -25346,7 +26262,11 @@
       <c r="A231" t="n">
         <v>11</v>
       </c>
-      <c r="B231" t="inlineStr"/>
+      <c r="B231" t="inlineStr">
+        <is>
+          <t>POST</t>
+        </is>
+      </c>
       <c r="C231" t="n">
         <v>27031</v>
       </c>
@@ -25454,7 +26374,11 @@
       <c r="A232" t="n">
         <v>11</v>
       </c>
-      <c r="B232" t="inlineStr"/>
+      <c r="B232" t="inlineStr">
+        <is>
+          <t>POST</t>
+        </is>
+      </c>
       <c r="C232" t="n">
         <v>27131</v>
       </c>
@@ -25562,7 +26486,11 @@
       <c r="A233" t="n">
         <v>11</v>
       </c>
-      <c r="B233" t="inlineStr"/>
+      <c r="B233" t="inlineStr">
+        <is>
+          <t>POST</t>
+        </is>
+      </c>
       <c r="C233" t="n">
         <v>27231</v>
       </c>
@@ -25670,7 +26598,11 @@
       <c r="A234" t="n">
         <v>11</v>
       </c>
-      <c r="B234" t="inlineStr"/>
+      <c r="B234" t="inlineStr">
+        <is>
+          <t>POST</t>
+        </is>
+      </c>
       <c r="C234" t="n">
         <v>27331</v>
       </c>
@@ -25778,7 +26710,11 @@
       <c r="A235" t="n">
         <v>11</v>
       </c>
-      <c r="B235" t="inlineStr"/>
+      <c r="B235" t="inlineStr">
+        <is>
+          <t>POST</t>
+        </is>
+      </c>
       <c r="C235" t="n">
         <v>27431</v>
       </c>
@@ -25886,7 +26822,11 @@
       <c r="A236" t="n">
         <v>11</v>
       </c>
-      <c r="B236" t="inlineStr"/>
+      <c r="B236" t="inlineStr">
+        <is>
+          <t>POST</t>
+        </is>
+      </c>
       <c r="C236" t="n">
         <v>27531</v>
       </c>
@@ -25994,7 +26934,11 @@
       <c r="A237" t="n">
         <v>11</v>
       </c>
-      <c r="B237" t="inlineStr"/>
+      <c r="B237" t="inlineStr">
+        <is>
+          <t>POST</t>
+        </is>
+      </c>
       <c r="C237" t="n">
         <v>27631</v>
       </c>
@@ -26102,7 +27046,11 @@
       <c r="A238" t="n">
         <v>11</v>
       </c>
-      <c r="B238" t="inlineStr"/>
+      <c r="B238" t="inlineStr">
+        <is>
+          <t>POST</t>
+        </is>
+      </c>
       <c r="C238" t="n">
         <v>27731</v>
       </c>
@@ -26210,7 +27158,11 @@
       <c r="A239" t="n">
         <v>11</v>
       </c>
-      <c r="B239" t="inlineStr"/>
+      <c r="B239" t="inlineStr">
+        <is>
+          <t>POST</t>
+        </is>
+      </c>
       <c r="C239" t="n">
         <v>27831</v>
       </c>
@@ -26318,7 +27270,11 @@
       <c r="A240" t="n">
         <v>11</v>
       </c>
-      <c r="B240" t="inlineStr"/>
+      <c r="B240" t="inlineStr">
+        <is>
+          <t>POST</t>
+        </is>
+      </c>
       <c r="C240" t="n">
         <v>27931</v>
       </c>
@@ -26426,7 +27382,11 @@
       <c r="A241" t="n">
         <v>11</v>
       </c>
-      <c r="B241" t="inlineStr"/>
+      <c r="B241" t="inlineStr">
+        <is>
+          <t>POST</t>
+        </is>
+      </c>
       <c r="C241" t="n">
         <v>28031</v>
       </c>
@@ -26534,7 +27494,11 @@
       <c r="A242" t="n">
         <v>11</v>
       </c>
-      <c r="B242" t="inlineStr"/>
+      <c r="B242" t="inlineStr">
+        <is>
+          <t>POST</t>
+        </is>
+      </c>
       <c r="C242" t="n">
         <v>28131</v>
       </c>
@@ -26642,7 +27606,11 @@
       <c r="A243" t="n">
         <v>11</v>
       </c>
-      <c r="B243" t="inlineStr"/>
+      <c r="B243" t="inlineStr">
+        <is>
+          <t>POST</t>
+        </is>
+      </c>
       <c r="C243" t="n">
         <v>28231</v>
       </c>
@@ -26750,7 +27718,11 @@
       <c r="A244" t="n">
         <v>11</v>
       </c>
-      <c r="B244" t="inlineStr"/>
+      <c r="B244" t="inlineStr">
+        <is>
+          <t>POST</t>
+        </is>
+      </c>
       <c r="C244" t="n">
         <v>28331</v>
       </c>
@@ -26858,7 +27830,11 @@
       <c r="A245" t="n">
         <v>11</v>
       </c>
-      <c r="B245" t="inlineStr"/>
+      <c r="B245" t="inlineStr">
+        <is>
+          <t>POST</t>
+        </is>
+      </c>
       <c r="C245" t="n">
         <v>28431</v>
       </c>
@@ -26966,7 +27942,11 @@
       <c r="A246" t="n">
         <v>11</v>
       </c>
-      <c r="B246" t="inlineStr"/>
+      <c r="B246" t="inlineStr">
+        <is>
+          <t>POST</t>
+        </is>
+      </c>
       <c r="C246" t="n">
         <v>28531</v>
       </c>
@@ -27074,7 +28054,11 @@
       <c r="A247" t="n">
         <v>11</v>
       </c>
-      <c r="B247" t="inlineStr"/>
+      <c r="B247" t="inlineStr">
+        <is>
+          <t>POST</t>
+        </is>
+      </c>
       <c r="C247" t="n">
         <v>28631</v>
       </c>
@@ -27182,7 +28166,11 @@
       <c r="A248" t="n">
         <v>11</v>
       </c>
-      <c r="B248" t="inlineStr"/>
+      <c r="B248" t="inlineStr">
+        <is>
+          <t>POST</t>
+        </is>
+      </c>
       <c r="C248" t="n">
         <v>28731</v>
       </c>
@@ -27290,7 +28278,11 @@
       <c r="A249" t="n">
         <v>11</v>
       </c>
-      <c r="B249" t="inlineStr"/>
+      <c r="B249" t="inlineStr">
+        <is>
+          <t>POST</t>
+        </is>
+      </c>
       <c r="C249" t="n">
         <v>28831</v>
       </c>
@@ -27398,7 +28390,11 @@
       <c r="A250" t="n">
         <v>11</v>
       </c>
-      <c r="B250" t="inlineStr"/>
+      <c r="B250" t="inlineStr">
+        <is>
+          <t>POST</t>
+        </is>
+      </c>
       <c r="C250" t="n">
         <v>28931</v>
       </c>
@@ -27506,7 +28502,11 @@
       <c r="A251" t="n">
         <v>11</v>
       </c>
-      <c r="B251" t="inlineStr"/>
+      <c r="B251" t="inlineStr">
+        <is>
+          <t>POST</t>
+        </is>
+      </c>
       <c r="C251" t="n">
         <v>29031</v>
       </c>
@@ -27614,7 +28614,11 @@
       <c r="A252" t="n">
         <v>11</v>
       </c>
-      <c r="B252" t="inlineStr"/>
+      <c r="B252" t="inlineStr">
+        <is>
+          <t>POST</t>
+        </is>
+      </c>
       <c r="C252" t="n">
         <v>29131</v>
       </c>
@@ -27722,7 +28726,11 @@
       <c r="A253" t="n">
         <v>11</v>
       </c>
-      <c r="B253" t="inlineStr"/>
+      <c r="B253" t="inlineStr">
+        <is>
+          <t>POST</t>
+        </is>
+      </c>
       <c r="C253" t="n">
         <v>29231</v>
       </c>
@@ -27830,7 +28838,11 @@
       <c r="A254" t="n">
         <v>11</v>
       </c>
-      <c r="B254" t="inlineStr"/>
+      <c r="B254" t="inlineStr">
+        <is>
+          <t>POST</t>
+        </is>
+      </c>
       <c r="C254" t="n">
         <v>29331</v>
       </c>
@@ -27938,7 +28950,11 @@
       <c r="A255" t="n">
         <v>11</v>
       </c>
-      <c r="B255" t="inlineStr"/>
+      <c r="B255" t="inlineStr">
+        <is>
+          <t>POST</t>
+        </is>
+      </c>
       <c r="C255" t="n">
         <v>29431</v>
       </c>
@@ -28046,7 +29062,11 @@
       <c r="A256" t="n">
         <v>11</v>
       </c>
-      <c r="B256" t="inlineStr"/>
+      <c r="B256" t="inlineStr">
+        <is>
+          <t>POST</t>
+        </is>
+      </c>
       <c r="C256" t="n">
         <v>29531</v>
       </c>
@@ -28154,7 +29174,11 @@
       <c r="A257" t="n">
         <v>11</v>
       </c>
-      <c r="B257" t="inlineStr"/>
+      <c r="B257" t="inlineStr">
+        <is>
+          <t>POST</t>
+        </is>
+      </c>
       <c r="C257" t="n">
         <v>29631</v>
       </c>
@@ -28262,7 +29286,11 @@
       <c r="A258" t="n">
         <v>11</v>
       </c>
-      <c r="B258" t="inlineStr"/>
+      <c r="B258" t="inlineStr">
+        <is>
+          <t>POST</t>
+        </is>
+      </c>
       <c r="C258" t="n">
         <v>29731</v>
       </c>
@@ -28370,7 +29398,11 @@
       <c r="A259" t="n">
         <v>11</v>
       </c>
-      <c r="B259" t="inlineStr"/>
+      <c r="B259" t="inlineStr">
+        <is>
+          <t>POST</t>
+        </is>
+      </c>
       <c r="C259" t="n">
         <v>29831</v>
       </c>
@@ -28478,7 +29510,11 @@
       <c r="A260" t="n">
         <v>11</v>
       </c>
-      <c r="B260" t="inlineStr"/>
+      <c r="B260" t="inlineStr">
+        <is>
+          <t>POST</t>
+        </is>
+      </c>
       <c r="C260" t="n">
         <v>29931</v>
       </c>
@@ -28586,7 +29622,11 @@
       <c r="A261" t="n">
         <v>11</v>
       </c>
-      <c r="B261" t="inlineStr"/>
+      <c r="B261" t="inlineStr">
+        <is>
+          <t>POST</t>
+        </is>
+      </c>
       <c r="C261" t="n">
         <v>30031</v>
       </c>
@@ -28694,7 +29734,11 @@
       <c r="A262" t="n">
         <v>11</v>
       </c>
-      <c r="B262" t="inlineStr"/>
+      <c r="B262" t="inlineStr">
+        <is>
+          <t>POST</t>
+        </is>
+      </c>
       <c r="C262" t="n">
         <v>30131</v>
       </c>
@@ -28802,7 +29846,11 @@
       <c r="A263" t="n">
         <v>12</v>
       </c>
-      <c r="B263" t="inlineStr"/>
+      <c r="B263" t="inlineStr">
+        <is>
+          <t>STOP</t>
+        </is>
+      </c>
       <c r="C263" t="n">
         <v>30141</v>
       </c>
@@ -28910,7 +29958,11 @@
       <c r="A264" t="n">
         <v>13</v>
       </c>
-      <c r="B264" t="inlineStr"/>
+      <c r="B264" t="inlineStr">
+        <is>
+          <t>CLOSE</t>
+        </is>
+      </c>
       <c r="C264" t="n">
         <v>30151</v>
       </c>
